--- a/data_tables/qol_enchant_text.xlsx
+++ b/data_tables/qol_enchant_text.xlsx
@@ -973,20 +973,20 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ATK -5%</t>
+          <t>ATK -10%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>dt22-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>The first game's wiki lists -10%</t>
+          <t>x86: 0x4f857e - 0x4f85a8 (int(stat / 10) is taken away; the same code serves the six stats, 0x4f8270 - 0x4f8fcf). The wiki of this game says -5%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
@@ -1135,20 +1135,20 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>DEF -5%</t>
+          <t>DEF -10%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>dt22-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>The first game's wiki lists -10%</t>
+          <t>x86: 0x4f857e - 0x4f85a8 (int(stat / 10) is taken away; the same code serves the six stats, 0x4f8270 - 0x4f8fcf). The wiki of this game says -5%</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
@@ -1297,20 +1297,20 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>INT -5%</t>
+          <t>INT -10%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>dt22-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The first game's wiki lists -10%</t>
+          <t>x86: 0x4f857e - 0x4f85a8 (int(stat / 10) is taken away; the same code serves the six stats, 0x4f8270 - 0x4f8fcf). The wiki of this game says -5%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
@@ -1459,20 +1459,20 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>RES -5%</t>
+          <t>RES -10%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>dt22-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>The first game's wiki lists -10%</t>
+          <t>x86: 0x4f857e - 0x4f85a8 (int(stat / 10) is taken away; the same code serves the six stats, 0x4f8270 - 0x4f8fcf). The wiki of this game says -5%</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
@@ -1621,20 +1621,20 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>DEX -5%</t>
+          <t>DEX -10%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>dt22-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The first game's wiki lists -10%</t>
+          <t>x86: 0x4f857e - 0x4f85a8 (int(stat / 10) is taken away; the same code serves the six stats, 0x4f8270 - 0x4f8fcf). The wiki of this game says -5%</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
@@ -1783,20 +1783,20 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>AGI -5%</t>
+          <t>AGI -10%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>dt22-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The first game's wiki lists -10%</t>
+          <t>x86: 0x4f857e - 0x4f85a8 (int(stat / 10) is taken away; the same code serves the six stats, 0x4f8270 - 0x4f8fcf). The wiki of this game says -5%</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
@@ -14312,7 +14312,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">
